--- a/_data/MVLS LTS ORCiD.xlsx
+++ b/_data/MVLS LTS ORCiD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29728"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gla-my.sharepoint.com/personal/emily_nordmann_glasgow_ac_uk/Documents/Teaching/psyteachR/mvls_lts/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="11_F25DC773A252ABDACC10485EA95868EA5ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BD28129-8C2F-4A54-9987-C7A0FF78F642}"/>
+  <xr:revisionPtr revIDLastSave="263" documentId="11_F25DC773A252ABDACC10485EA95868EA5ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59D7FE63-DD6E-4767-9376-6A8B5F94FB5C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="140">
   <si>
     <t>Name</t>
   </si>
@@ -104,6 +104,12 @@
     <t>0000-0001-8910-6490</t>
   </si>
   <si>
+    <t>Alison Reid</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0001-9734-2143</t>
+  </si>
+  <si>
     <t>Laura Richmond</t>
   </si>
   <si>
@@ -444,6 +450,12 @@
   </si>
   <si>
     <t>https://orcid.org/my-orcid?orcid=0009-0002-4183-600X</t>
+  </si>
+  <si>
+    <t>Emilie Law</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0009-0009-7322-675X</t>
   </si>
 </sst>
 </file>
@@ -790,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.28515625" customWidth="1"/>
@@ -902,29 +914,29 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15">
       <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
         <v>25</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>26</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15">
       <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
         <v>28</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -935,7 +947,7 @@
         <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>31</v>
@@ -946,9 +958,9 @@
         <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -957,9 +969,9 @@
         <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
         <v>35</v>
       </c>
     </row>
@@ -968,7 +980,7 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>37</v>
@@ -979,7 +991,7 @@
         <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>39</v>
@@ -990,7 +1002,7 @@
         <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>41</v>
@@ -1001,18 +1013,18 @@
         <v>42</v>
       </c>
       <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15">
       <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
         <v>45</v>
-      </c>
-      <c r="B20" t="s">
-        <v>43</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>46</v>
@@ -1023,7 +1035,7 @@
         <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>48</v>
@@ -1034,7 +1046,7 @@
         <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>50</v>
@@ -1045,20 +1057,20 @@
         <v>51</v>
       </c>
       <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15">
       <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" t="s">
         <v>54</v>
       </c>
-      <c r="B24" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="1" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1067,18 +1079,18 @@
         <v>56</v>
       </c>
       <c r="B25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15">
       <c r="A26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" t="s">
         <v>59</v>
-      </c>
-      <c r="B26" t="s">
-        <v>57</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>60</v>
@@ -1089,7 +1101,7 @@
         <v>61</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>62</v>
@@ -1100,7 +1112,7 @@
         <v>63</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>64</v>
@@ -1111,7 +1123,7 @@
         <v>65</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>66</v>
@@ -1122,7 +1134,7 @@
         <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>68</v>
@@ -1133,18 +1145,18 @@
         <v>69</v>
       </c>
       <c r="B31" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C31" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15">
       <c r="A32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" t="s">
         <v>72</v>
-      </c>
-      <c r="B32" t="s">
-        <v>70</v>
       </c>
       <c r="C32" t="s">
         <v>73</v>
@@ -1155,9 +1167,9 @@
         <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1166,7 +1178,7 @@
         <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>77</v>
@@ -1177,7 +1189,7 @@
         <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>79</v>
@@ -1188,7 +1200,7 @@
         <v>80</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>81</v>
@@ -1199,9 +1211,9 @@
         <v>82</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1210,20 +1222,20 @@
         <v>84</v>
       </c>
       <c r="B38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="C38" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15">
       <c r="A39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" t="s">
         <v>87</v>
       </c>
-      <c r="B39" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s">
         <v>88</v>
       </c>
     </row>
@@ -1232,7 +1244,7 @@
         <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>90</v>
@@ -1243,7 +1255,7 @@
         <v>91</v>
       </c>
       <c r="B41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>92</v>
@@ -1254,7 +1266,7 @@
         <v>93</v>
       </c>
       <c r="B42" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>94</v>
@@ -1265,7 +1277,7 @@
         <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>96</v>
@@ -1276,7 +1288,7 @@
         <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>98</v>
@@ -1287,7 +1299,7 @@
         <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>100</v>
@@ -1298,7 +1310,7 @@
         <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>102</v>
@@ -1309,7 +1321,7 @@
         <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>104</v>
@@ -1320,7 +1332,7 @@
         <v>105</v>
       </c>
       <c r="B48" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>106</v>
@@ -1331,7 +1343,7 @@
         <v>107</v>
       </c>
       <c r="B49" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>108</v>
@@ -1342,18 +1354,18 @@
         <v>109</v>
       </c>
       <c r="B50" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15">
       <c r="A51" t="s">
+        <v>111</v>
+      </c>
+      <c r="B51" t="s">
         <v>112</v>
-      </c>
-      <c r="B51" t="s">
-        <v>110</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>113</v>
@@ -1364,7 +1376,7 @@
         <v>114</v>
       </c>
       <c r="B52" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>115</v>
@@ -1375,7 +1387,7 @@
         <v>116</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>117</v>
@@ -1386,7 +1398,7 @@
         <v>118</v>
       </c>
       <c r="B54" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>119</v>
@@ -1397,7 +1409,7 @@
         <v>120</v>
       </c>
       <c r="B55" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>121</v>
@@ -1419,21 +1431,21 @@
         <v>124</v>
       </c>
       <c r="B57" t="s">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="15">
       <c r="A58" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" t="s">
+        <v>112</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B58" t="s">
-        <v>85</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="15">
@@ -1441,18 +1453,18 @@
         <v>127</v>
       </c>
       <c r="B59" t="s">
+        <v>87</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="15">
       <c r="A60" t="s">
+        <v>129</v>
+      </c>
+      <c r="B60" t="s">
         <v>130</v>
-      </c>
-      <c r="B60" t="s">
-        <v>20</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>131</v>
@@ -1463,7 +1475,7 @@
         <v>132</v>
       </c>
       <c r="B61" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>133</v>
@@ -1474,72 +1486,96 @@
         <v>134</v>
       </c>
       <c r="B62" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>135</v>
       </c>
     </row>
+    <row r="63" spans="1:3" ht="15">
+      <c r="A63" t="s">
+        <v>136</v>
+      </c>
+      <c r="B63" t="s">
+        <v>112</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="15">
+      <c r="A64" t="s">
+        <v>138</v>
+      </c>
+      <c r="B64" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C51">
-    <sortCondition ref="B2:B51"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C52">
+    <sortCondition ref="B2:B52"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="C11" r:id="rId1" xr:uid="{60EFD2F2-20D8-4632-AE79-0B4039007552}"/>
-    <hyperlink ref="C39" r:id="rId2" xr:uid="{905A93DF-37AB-479C-AFB1-7AFE9087B707}"/>
-    <hyperlink ref="C25" r:id="rId3" xr:uid="{3B0656E1-6D55-4D3B-A91B-E66CBD3EC3D1}"/>
-    <hyperlink ref="C40" r:id="rId4" xr:uid="{86BABA8B-BE9E-40DC-89A8-BAAAEA2F6933}"/>
+    <hyperlink ref="C12" r:id="rId1" xr:uid="{60EFD2F2-20D8-4632-AE79-0B4039007552}"/>
+    <hyperlink ref="C40" r:id="rId2" xr:uid="{905A93DF-37AB-479C-AFB1-7AFE9087B707}"/>
+    <hyperlink ref="C26" r:id="rId3" xr:uid="{3B0656E1-6D55-4D3B-A91B-E66CBD3EC3D1}"/>
+    <hyperlink ref="C41" r:id="rId4" xr:uid="{86BABA8B-BE9E-40DC-89A8-BAAAEA2F6933}"/>
     <hyperlink ref="C5" r:id="rId5" xr:uid="{1F56D623-FD9B-46F4-AD94-1FE95F0B041B}"/>
-    <hyperlink ref="C41" r:id="rId6" xr:uid="{01C62254-C9AE-42C1-83DE-B2B9CEDA063D}"/>
+    <hyperlink ref="C42" r:id="rId6" xr:uid="{01C62254-C9AE-42C1-83DE-B2B9CEDA063D}"/>
     <hyperlink ref="C6" r:id="rId7" xr:uid="{6F217E1C-1E80-493A-AD36-C82F58DAB0E7}"/>
-    <hyperlink ref="C26" r:id="rId8" xr:uid="{78E58C1B-4566-41EE-BE2F-2D15E76060D7}"/>
-    <hyperlink ref="C12" r:id="rId9" xr:uid="{853DA834-5C5C-2A42-987E-FAE24AF2B769}"/>
-    <hyperlink ref="C15" r:id="rId10" xr:uid="{44759F3A-04AC-420D-9DDB-7D6AB2D56272}"/>
-    <hyperlink ref="C33" r:id="rId11" xr:uid="{DBDCD06D-2923-4218-BC97-ABE03390F1D7}"/>
-    <hyperlink ref="C34" r:id="rId12" xr:uid="{2AB62B2B-68E1-40FD-B878-E1B53BE55C54}"/>
-    <hyperlink ref="C19" r:id="rId13" xr:uid="{1FE273A7-C2F0-4349-9B1A-4442668BA296}"/>
-    <hyperlink ref="C35" r:id="rId14" xr:uid="{9381CA16-CF22-4437-ACD7-1E1796619196}"/>
-    <hyperlink ref="C42" r:id="rId15" xr:uid="{8A309B9A-E247-4CBE-87BB-B85B0A69E7D8}"/>
-    <hyperlink ref="C16" r:id="rId16" xr:uid="{70D6EB93-C68C-4CDC-BF76-F41A8E2104DE}"/>
-    <hyperlink ref="C36" r:id="rId17" xr:uid="{4848D5FD-F053-4486-8E3E-D89C72341827}"/>
-    <hyperlink ref="C17" r:id="rId18" xr:uid="{8F35F983-AFB9-48AE-8283-EE20E0D257FF}"/>
-    <hyperlink ref="C43" r:id="rId19" xr:uid="{2E7B406A-B501-4CFA-810E-97CD43405EB3}"/>
-    <hyperlink ref="C44" r:id="rId20" xr:uid="{42C99594-AAE8-4E35-91FC-5AB94011BC96}"/>
+    <hyperlink ref="C27" r:id="rId8" xr:uid="{78E58C1B-4566-41EE-BE2F-2D15E76060D7}"/>
+    <hyperlink ref="C13" r:id="rId9" xr:uid="{853DA834-5C5C-2A42-987E-FAE24AF2B769}"/>
+    <hyperlink ref="C16" r:id="rId10" xr:uid="{44759F3A-04AC-420D-9DDB-7D6AB2D56272}"/>
+    <hyperlink ref="C34" r:id="rId11" xr:uid="{DBDCD06D-2923-4218-BC97-ABE03390F1D7}"/>
+    <hyperlink ref="C35" r:id="rId12" xr:uid="{2AB62B2B-68E1-40FD-B878-E1B53BE55C54}"/>
+    <hyperlink ref="C20" r:id="rId13" xr:uid="{1FE273A7-C2F0-4349-9B1A-4442668BA296}"/>
+    <hyperlink ref="C36" r:id="rId14" xr:uid="{9381CA16-CF22-4437-ACD7-1E1796619196}"/>
+    <hyperlink ref="C43" r:id="rId15" xr:uid="{8A309B9A-E247-4CBE-87BB-B85B0A69E7D8}"/>
+    <hyperlink ref="C17" r:id="rId16" xr:uid="{70D6EB93-C68C-4CDC-BF76-F41A8E2104DE}"/>
+    <hyperlink ref="C37" r:id="rId17" xr:uid="{4848D5FD-F053-4486-8E3E-D89C72341827}"/>
+    <hyperlink ref="C18" r:id="rId18" xr:uid="{8F35F983-AFB9-48AE-8283-EE20E0D257FF}"/>
+    <hyperlink ref="C44" r:id="rId19" xr:uid="{2E7B406A-B501-4CFA-810E-97CD43405EB3}"/>
+    <hyperlink ref="C45" r:id="rId20" xr:uid="{42C99594-AAE8-4E35-91FC-5AB94011BC96}"/>
     <hyperlink ref="C7" r:id="rId21" xr:uid="{FEEF8F34-0FC0-4F46-9A43-8C7A538DDB05}"/>
     <hyperlink ref="C3" r:id="rId22" xr:uid="{44209C97-1064-412A-A07E-09A8319F0DC3}"/>
-    <hyperlink ref="C45" r:id="rId23" xr:uid="{E3C2BCAA-B2C5-4140-AFAB-699F12F824F8}"/>
-    <hyperlink ref="C20" r:id="rId24" xr:uid="{6775C434-C635-41C4-A4A2-85E4FC7BF7B4}"/>
-    <hyperlink ref="C46" r:id="rId25" xr:uid="{9B49F270-4E7E-4719-B7C6-A6C10D0755E1}"/>
-    <hyperlink ref="C47" r:id="rId26" xr:uid="{39424440-C765-4B0E-A77A-F13B8E6025C0}"/>
-    <hyperlink ref="C48" r:id="rId27" xr:uid="{5E9507EB-C8C0-4121-AAC7-F797B1919E5B}"/>
-    <hyperlink ref="C21" r:id="rId28" xr:uid="{240C280F-C6A6-4AAF-B749-C521E8C36A54}"/>
-    <hyperlink ref="C22" r:id="rId29" xr:uid="{D9FF37C8-1533-4CAF-8493-CEE43B120B13}"/>
-    <hyperlink ref="C18" r:id="rId30" xr:uid="{5E303B2A-86FF-4460-A167-90ECDB6A9B0E}"/>
-    <hyperlink ref="C13" r:id="rId31" xr:uid="{DCF47709-2C3C-7141-8672-BC6FE078F3C8}"/>
-    <hyperlink ref="C50" r:id="rId32" xr:uid="{C6722E39-8D6E-498B-956C-E13CEF15DD91}"/>
-    <hyperlink ref="C51" r:id="rId33" xr:uid="{B352DAFD-8E59-403E-9531-64C53F63C44F}"/>
+    <hyperlink ref="C46" r:id="rId23" xr:uid="{E3C2BCAA-B2C5-4140-AFAB-699F12F824F8}"/>
+    <hyperlink ref="C21" r:id="rId24" xr:uid="{6775C434-C635-41C4-A4A2-85E4FC7BF7B4}"/>
+    <hyperlink ref="C47" r:id="rId25" xr:uid="{9B49F270-4E7E-4719-B7C6-A6C10D0755E1}"/>
+    <hyperlink ref="C48" r:id="rId26" xr:uid="{39424440-C765-4B0E-A77A-F13B8E6025C0}"/>
+    <hyperlink ref="C49" r:id="rId27" xr:uid="{5E9507EB-C8C0-4121-AAC7-F797B1919E5B}"/>
+    <hyperlink ref="C22" r:id="rId28" xr:uid="{240C280F-C6A6-4AAF-B749-C521E8C36A54}"/>
+    <hyperlink ref="C23" r:id="rId29" xr:uid="{D9FF37C8-1533-4CAF-8493-CEE43B120B13}"/>
+    <hyperlink ref="C19" r:id="rId30" xr:uid="{5E303B2A-86FF-4460-A167-90ECDB6A9B0E}"/>
+    <hyperlink ref="C14" r:id="rId31" xr:uid="{DCF47709-2C3C-7141-8672-BC6FE078F3C8}"/>
+    <hyperlink ref="C51" r:id="rId32" xr:uid="{C6722E39-8D6E-498B-956C-E13CEF15DD91}"/>
+    <hyperlink ref="C52" r:id="rId33" xr:uid="{B352DAFD-8E59-403E-9531-64C53F63C44F}"/>
     <hyperlink ref="C4" r:id="rId34" xr:uid="{57AE4192-3C88-48E0-8269-EB3CD1E6C2A8}"/>
-    <hyperlink ref="C24" r:id="rId35" xr:uid="{BCE8B85C-7F7F-4303-ADF2-DC9FFE1ACA40}"/>
-    <hyperlink ref="C27" r:id="rId36" xr:uid="{FCCF507F-3E72-4788-BAF6-6DA009D7394C}"/>
-    <hyperlink ref="C28" r:id="rId37" xr:uid="{A289D90F-20D8-450E-9AB0-557D85EA314F}"/>
-    <hyperlink ref="C29" r:id="rId38" xr:uid="{26E44FBF-4211-4D7A-A9A8-A4D19F2C8064}"/>
-    <hyperlink ref="C30" r:id="rId39" xr:uid="{312F4EBC-D623-4233-A423-601AA8543EEC}"/>
+    <hyperlink ref="C25" r:id="rId35" xr:uid="{BCE8B85C-7F7F-4303-ADF2-DC9FFE1ACA40}"/>
+    <hyperlink ref="C28" r:id="rId36" xr:uid="{FCCF507F-3E72-4788-BAF6-6DA009D7394C}"/>
+    <hyperlink ref="C29" r:id="rId37" xr:uid="{A289D90F-20D8-450E-9AB0-557D85EA314F}"/>
+    <hyperlink ref="C30" r:id="rId38" xr:uid="{26E44FBF-4211-4D7A-A9A8-A4D19F2C8064}"/>
+    <hyperlink ref="C31" r:id="rId39" xr:uid="{312F4EBC-D623-4233-A423-601AA8543EEC}"/>
     <hyperlink ref="C2" r:id="rId40" xr:uid="{D5CE1D64-E6A0-489F-80ED-CD86A9700059}"/>
-    <hyperlink ref="C49" r:id="rId41" xr:uid="{BEDA0D96-EA07-4DA1-AA12-AF21965BE98F}"/>
+    <hyperlink ref="C50" r:id="rId41" xr:uid="{BEDA0D96-EA07-4DA1-AA12-AF21965BE98F}"/>
     <hyperlink ref="C8" r:id="rId42" xr:uid="{193C1629-FF53-4D82-89AC-4951C024A328}"/>
     <hyperlink ref="C9" r:id="rId43" xr:uid="{99D04A76-6CF1-4E21-8E24-08577B6D8EDD}"/>
-    <hyperlink ref="C23" r:id="rId44" xr:uid="{5BD7097C-F4F9-4E7C-928E-9F7DB32C56BE}"/>
-    <hyperlink ref="C52" r:id="rId45" xr:uid="{D9D7F3DC-EB7B-496A-957B-D642222B2184}"/>
-    <hyperlink ref="C53" r:id="rId46" xr:uid="{57026629-D559-44AA-99C0-D6812C6C5753}"/>
-    <hyperlink ref="C54" r:id="rId47" xr:uid="{5502A002-2A4E-41BD-8753-3F8E6A3FE3AD}"/>
-    <hyperlink ref="C55" r:id="rId48" xr:uid="{E40631A0-C61A-4DA4-B1AD-AF3EEC89DC51}"/>
-    <hyperlink ref="C56" r:id="rId49" xr:uid="{6B54A3F6-9175-4567-9381-B34FE03B16B6}"/>
-    <hyperlink ref="C57" r:id="rId50" xr:uid="{CC0D3221-A564-41AD-89C3-B9BD2DB862AF}"/>
-    <hyperlink ref="C58" r:id="rId51" xr:uid="{99B08B75-DF0E-4727-AA58-7972572A4E0F}"/>
-    <hyperlink ref="C59" r:id="rId52" xr:uid="{051C51F6-F07A-4545-83B8-86BF9E184DDC}"/>
-    <hyperlink ref="C60" r:id="rId53" xr:uid="{E81E296F-58C8-46D4-AF45-51F0E6BB9EFE}"/>
-    <hyperlink ref="C61" r:id="rId54" xr:uid="{6ED15BE1-DB86-44F1-9E4E-AEF7035A9A0A}"/>
-    <hyperlink ref="C62" r:id="rId55" xr:uid="{E0165319-1A0E-477E-B52D-E0057A44F615}"/>
+    <hyperlink ref="C24" r:id="rId44" xr:uid="{5BD7097C-F4F9-4E7C-928E-9F7DB32C56BE}"/>
+    <hyperlink ref="C53" r:id="rId45" xr:uid="{D9D7F3DC-EB7B-496A-957B-D642222B2184}"/>
+    <hyperlink ref="C54" r:id="rId46" xr:uid="{57026629-D559-44AA-99C0-D6812C6C5753}"/>
+    <hyperlink ref="C55" r:id="rId47" xr:uid="{5502A002-2A4E-41BD-8753-3F8E6A3FE3AD}"/>
+    <hyperlink ref="C56" r:id="rId48" xr:uid="{E40631A0-C61A-4DA4-B1AD-AF3EEC89DC51}"/>
+    <hyperlink ref="C57" r:id="rId49" xr:uid="{6B54A3F6-9175-4567-9381-B34FE03B16B6}"/>
+    <hyperlink ref="C58" r:id="rId50" xr:uid="{CC0D3221-A564-41AD-89C3-B9BD2DB862AF}"/>
+    <hyperlink ref="C59" r:id="rId51" xr:uid="{99B08B75-DF0E-4727-AA58-7972572A4E0F}"/>
+    <hyperlink ref="C60" r:id="rId52" xr:uid="{051C51F6-F07A-4545-83B8-86BF9E184DDC}"/>
+    <hyperlink ref="C61" r:id="rId53" xr:uid="{E81E296F-58C8-46D4-AF45-51F0E6BB9EFE}"/>
+    <hyperlink ref="C62" r:id="rId54" xr:uid="{6ED15BE1-DB86-44F1-9E4E-AEF7035A9A0A}"/>
+    <hyperlink ref="C63" r:id="rId55" xr:uid="{E0165319-1A0E-477E-B52D-E0057A44F615}"/>
+    <hyperlink ref="C10" r:id="rId56" xr:uid="{708A4E17-0586-427D-B106-9DB06F0F1341}"/>
+    <hyperlink ref="C64" r:id="rId57" xr:uid="{418027A3-A711-41F9-A5A7-CEEDCA43C269}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/_data/MVLS LTS ORCiD.xlsx
+++ b/_data/MVLS LTS ORCiD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10306"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gla-my.sharepoint.com/personal/emily_nordmann_glasgow_ac_uk/Documents/Teaching/psyteachR/mvls_lts/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="11_F25DC773A252ABDACC10485EA95868EA5ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D90637A-78D5-4520-A1BB-7CA9BBDBC6B7}"/>
+  <xr:revisionPtr revIDLastSave="268" documentId="11_F25DC773A252ABDACC10485EA95868EA5ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB0E40E2-7291-C84E-88CF-F6786D0B1554}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="142">
   <si>
     <t>Name</t>
   </si>
@@ -456,13 +456,19 @@
   </si>
   <si>
     <t>https://orcid.org/0009-0009-7322-675X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ourania Varsou </t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-7789-1185</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -802,15 +808,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C64"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <dimension ref="A1:C65"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" customWidth="1"/>
-    <col min="2" max="2" width="54.5703125" customWidth="1"/>
-    <col min="3" max="3" width="38.42578125" customWidth="1"/>
+    <col min="1" max="1" width="25.2890625" customWidth="1"/>
+    <col min="2" max="2" width="54.61328125" customWidth="1"/>
+    <col min="3" max="3" width="38.47265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -821,7 +827,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -832,7 +838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -843,7 +849,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -854,7 +860,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -865,7 +871,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -876,7 +882,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -887,7 +893,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -898,7 +904,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -909,7 +915,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -920,7 +926,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -931,7 +937,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -942,7 +948,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -953,7 +959,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -964,7 +970,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -975,7 +981,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -986,7 +992,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -997,7 +1003,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1008,7 +1014,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1019,7 +1025,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1030,7 +1036,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -1041,7 +1047,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -1052,7 +1058,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -1063,7 +1069,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1074,7 +1080,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -1085,7 +1091,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1096,7 +1102,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1107,7 +1113,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -1118,7 +1124,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>65</v>
       </c>
@@ -1129,7 +1135,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -1140,7 +1146,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>69</v>
       </c>
@@ -1151,7 +1157,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>71</v>
       </c>
@@ -1162,7 +1168,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -1173,7 +1179,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -1184,7 +1190,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>78</v>
       </c>
@@ -1195,7 +1201,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>80</v>
       </c>
@@ -1206,7 +1212,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -1217,7 +1223,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -1228,7 +1234,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -1239,7 +1245,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1250,7 +1256,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1261,7 +1267,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -1272,7 +1278,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>95</v>
       </c>
@@ -1283,7 +1289,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>97</v>
       </c>
@@ -1294,7 +1300,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>99</v>
       </c>
@@ -1305,7 +1311,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -1316,7 +1322,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>103</v>
       </c>
@@ -1327,7 +1333,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>105</v>
       </c>
@@ -1338,7 +1344,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>107</v>
       </c>
@@ -1349,7 +1355,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>109</v>
       </c>
@@ -1360,7 +1366,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>111</v>
       </c>
@@ -1371,7 +1377,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>114</v>
       </c>
@@ -1382,7 +1388,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>116</v>
       </c>
@@ -1393,7 +1399,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>118</v>
       </c>
@@ -1404,7 +1410,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>120</v>
       </c>
@@ -1415,7 +1421,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>122</v>
       </c>
@@ -1426,7 +1432,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>124</v>
       </c>
@@ -1437,7 +1443,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>126</v>
       </c>
@@ -1448,7 +1454,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>127</v>
       </c>
@@ -1459,7 +1465,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>129</v>
       </c>
@@ -1470,7 +1476,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>132</v>
       </c>
@@ -1481,7 +1487,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>134</v>
       </c>
@@ -1492,7 +1498,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>136</v>
       </c>
@@ -1503,7 +1509,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>138</v>
       </c>
@@ -1512,6 +1518,17 @@
       </c>
       <c r="C64" s="1" t="s">
         <v>139</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>140</v>
+      </c>
+      <c r="B65" t="s">
+        <v>112</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1576,6 +1593,7 @@
     <hyperlink ref="C63" r:id="rId55" xr:uid="{E0165319-1A0E-477E-B52D-E0057A44F615}"/>
     <hyperlink ref="C10" r:id="rId56" xr:uid="{708A4E17-0586-427D-B106-9DB06F0F1341}"/>
     <hyperlink ref="C64" r:id="rId57" xr:uid="{418027A3-A711-41F9-A5A7-CEEDCA43C269}"/>
+    <hyperlink ref="C65" r:id="rId58" xr:uid="{2A5635ED-DF81-EA4B-8D6E-86E01201A208}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/_data/MVLS LTS ORCiD.xlsx
+++ b/_data/MVLS LTS ORCiD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30203"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gla-my.sharepoint.com/personal/emily_nordmann_glasgow_ac_uk/Documents/Teaching/psyteachR/mvls_lts/_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="271" documentId="11_F25DC773A252ABDACC10485EA95868EA5ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{421F3126-ECCB-4980-8777-C28D3C2DC144}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53DA4A6A-76E6-433A-A22F-A0B8FBCD6F50}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,15 +36,40 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="149">
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Start time</t>
+  </si>
+  <si>
+    <t>Completion time</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>School</t>
-  </si>
-  <si>
-    <t>ORCiD</t>
+    <t>In which School are you based?</t>
+  </si>
+  <si>
+    <t>Please provide your ORCiD in the form https://orcid.org/0000-0002-0806-1081
+Please don't write anything else in this box, just drop in the full URL</t>
+  </si>
+  <si>
+    <t>Emily.Nordmann@glasgow.ac.uk</t>
+  </si>
+  <si>
+    <t>Emily Nordmann</t>
+  </si>
+  <si>
+    <t>School of Psychology and Neuroscience</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-0806-1081</t>
   </si>
   <si>
     <t>Susan Lindsay</t>
@@ -101,7 +126,7 @@
     <t xml:space="preserve">School of Biodiversity, One Health and Veterinary Medicine </t>
   </si>
   <si>
-    <t>0000-0001-8910-6490</t>
+    <t>https://orcid.org/0000-0001-8910-6490</t>
   </si>
   <si>
     <t>Alison Reid</t>
@@ -296,15 +321,6 @@
     <t>https://orcid.org/0009-0007-3998-9329</t>
   </si>
   <si>
-    <t>Emily Nordmann</t>
-  </si>
-  <si>
-    <t>School of Psychology and Neuroscience</t>
-  </si>
-  <si>
-    <t>https://orcid.org/0000-0002-0806-1081</t>
-  </si>
-  <si>
     <t>Ashley Robertson</t>
   </si>
   <si>
@@ -437,7 +453,7 @@
     <t>Nicholas Rudzik</t>
   </si>
   <si>
-    <t>0009-0005-8819-0826</t>
+    <t>https://orcid.org/0009-0005-8819-0826</t>
   </si>
   <si>
     <t>Steven McNair</t>
@@ -449,7 +465,7 @@
     <t>Dougie Marks</t>
   </si>
   <si>
-    <t>https://orcid.org/my-orcid?orcid=0009-0002-4183-600X</t>
+    <t>https://orcid.org/0009-0002-4183-600X</t>
   </si>
   <si>
     <t>Emilie Law</t>
@@ -474,7 +490,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,19 +505,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="2">
@@ -523,22 +526,37 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -549,6 +567,77 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:G66" totalsRowShown="0">
+  <autoFilter ref="A1:G66" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="4">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="id"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="startDate"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="submitDate"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="3">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="responder"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="2">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="responderName"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="In which School are you based?" dataDxfId="1">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r9b1a8c7c6e164d7ebd8daf43a0a4c46c"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Please provide your ORCiD in the form https://orcid.org/0000-0002-0806-1081_x000a__x000a_Please don't write anything else in this box, just drop in the full URL" dataDxfId="0">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="ra1a05d35ca8c4c9281d74aaac9d7c4ab"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <extLst>
+    <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
+      <xlmsforms:msForm id="KVxybjp2UE-B8i4lTwEzyKAHhjrab3lLkx60RR1iKjNUOTVNTEMwVE02SEhMQ0ZZODExQktLVThBSiQlQCNjPTEu" isFormConnected="1" maxResponseId="2" latestEventMarker="1">
+        <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>responder</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>responderName</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r9b1a8c7c6e164d7ebd8daf43a0a4c46c</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>ra1a05d35ca8c4c9281d74aaac9d7c4ab</xlmsforms:syncedQuestionId>
+      </xlmsforms:msForm>
+    </ext>
+  </extLst>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -597,9 +686,9 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -627,14 +716,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -662,6 +768,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -814,805 +937,957 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C66"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <dimension ref="A1:G66"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" customWidth="1"/>
-    <col min="2" max="2" width="54.5703125" customWidth="1"/>
-    <col min="3" max="3" width="38.42578125" customWidth="1"/>
+    <col min="1" max="7" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46189.353703703702</v>
+      </c>
+      <c r="C2" s="2">
+        <v>46189.353900462964</v>
+      </c>
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="F2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="3"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
+      <c r="G3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1" t="s">
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="3"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="1" t="s">
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="3"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
+      <c r="F5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="1" t="s">
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="3"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
+      <c r="F6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
+      <c r="G6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="1" t="s">
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="3"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
+      <c r="F7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="1" t="s">
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="3"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
+      <c r="F8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="3"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
+    <row r="10" spans="1:7">
+      <c r="A10" s="3"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B12" t="s">
+      <c r="F10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="G10" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
+    <row r="11" spans="1:7">
+      <c r="A11" s="3"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B13" t="s">
+      <c r="F11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="G11" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
+    <row r="12" spans="1:7">
+      <c r="A12" s="3"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B14" t="s">
+      <c r="F12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="3"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="3"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="3"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="3"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="3"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="3"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="3"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="3"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="3"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="3"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="3"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="3"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="3"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="3"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="3"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="3"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="3"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="3"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="3"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="3"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="3"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="3"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="3"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="3"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="3"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="3"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="3"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="3"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="3"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="3"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="3"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="3"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="3"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="3"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="3"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="3"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="3"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="3"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="3"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="3"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="3"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="G54" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="3"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="3"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="G56" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="3"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="G57" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="3"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="3"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="3"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="3"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="G61" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="3"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="3"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="3"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>65</v>
-      </c>
-      <c r="B29" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
+      <c r="G64" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="3"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="3"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>69</v>
-      </c>
-      <c r="B31" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>76</v>
-      </c>
-      <c r="B34" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>78</v>
-      </c>
-      <c r="B35" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>80</v>
-      </c>
-      <c r="B36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
-        <v>82</v>
-      </c>
-      <c r="B37" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
-        <v>84</v>
-      </c>
-      <c r="B38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
-        <v>86</v>
-      </c>
-      <c r="B39" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" t="s">
-        <v>89</v>
-      </c>
-      <c r="B40" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" t="s">
-        <v>91</v>
-      </c>
-      <c r="B41" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
-        <v>93</v>
-      </c>
-      <c r="B42" t="s">
-        <v>87</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
-        <v>95</v>
-      </c>
-      <c r="B43" t="s">
-        <v>87</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
-        <v>97</v>
-      </c>
-      <c r="B44" t="s">
-        <v>87</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
-        <v>99</v>
-      </c>
-      <c r="B45" t="s">
-        <v>87</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
-        <v>101</v>
-      </c>
-      <c r="B46" t="s">
-        <v>87</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
-        <v>103</v>
-      </c>
-      <c r="B47" t="s">
-        <v>87</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
-        <v>105</v>
-      </c>
-      <c r="B48" t="s">
-        <v>87</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
-        <v>107</v>
-      </c>
-      <c r="B49" t="s">
-        <v>87</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
-        <v>109</v>
-      </c>
-      <c r="B50" t="s">
-        <v>87</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
-        <v>111</v>
-      </c>
-      <c r="B51" t="s">
-        <v>112</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
-        <v>114</v>
-      </c>
-      <c r="B52" t="s">
-        <v>112</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
-        <v>116</v>
-      </c>
-      <c r="B53" t="s">
-        <v>87</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" t="s">
-        <v>118</v>
-      </c>
-      <c r="B54" t="s">
-        <v>20</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" t="s">
-        <v>120</v>
-      </c>
-      <c r="B55" t="s">
-        <v>87</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" t="s">
-        <v>122</v>
-      </c>
-      <c r="B56" t="s">
-        <v>20</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" t="s">
-        <v>124</v>
-      </c>
-      <c r="B57" t="s">
-        <v>20</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" t="s">
-        <v>126</v>
-      </c>
-      <c r="B58" t="s">
-        <v>112</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" t="s">
-        <v>127</v>
-      </c>
-      <c r="B59" t="s">
-        <v>87</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" t="s">
-        <v>129</v>
-      </c>
-      <c r="B60" t="s">
-        <v>130</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" t="s">
-        <v>132</v>
-      </c>
-      <c r="B61" t="s">
-        <v>20</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" t="s">
-        <v>134</v>
-      </c>
-      <c r="B62" t="s">
-        <v>87</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>136</v>
-      </c>
-      <c r="B63" t="s">
-        <v>112</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" t="s">
-        <v>138</v>
-      </c>
-      <c r="B64" t="s">
-        <v>20</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" t="s">
-        <v>140</v>
-      </c>
-      <c r="B65" t="s">
-        <v>112</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
-        <v>142</v>
-      </c>
-      <c r="B66" t="s">
-        <v>59</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>143</v>
+      <c r="G66" s="4" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C52">
-    <sortCondition ref="B2:B52"/>
-  </sortState>
   <hyperlinks>
-    <hyperlink ref="C12" r:id="rId1" xr:uid="{60EFD2F2-20D8-4632-AE79-0B4039007552}"/>
-    <hyperlink ref="C40" r:id="rId2" xr:uid="{905A93DF-37AB-479C-AFB1-7AFE9087B707}"/>
-    <hyperlink ref="C26" r:id="rId3" xr:uid="{3B0656E1-6D55-4D3B-A91B-E66CBD3EC3D1}"/>
-    <hyperlink ref="C41" r:id="rId4" xr:uid="{86BABA8B-BE9E-40DC-89A8-BAAAEA2F6933}"/>
-    <hyperlink ref="C5" r:id="rId5" xr:uid="{1F56D623-FD9B-46F4-AD94-1FE95F0B041B}"/>
-    <hyperlink ref="C42" r:id="rId6" xr:uid="{01C62254-C9AE-42C1-83DE-B2B9CEDA063D}"/>
-    <hyperlink ref="C6" r:id="rId7" xr:uid="{6F217E1C-1E80-493A-AD36-C82F58DAB0E7}"/>
-    <hyperlink ref="C27" r:id="rId8" xr:uid="{78E58C1B-4566-41EE-BE2F-2D15E76060D7}"/>
-    <hyperlink ref="C13" r:id="rId9" xr:uid="{853DA834-5C5C-2A42-987E-FAE24AF2B769}"/>
-    <hyperlink ref="C16" r:id="rId10" xr:uid="{44759F3A-04AC-420D-9DDB-7D6AB2D56272}"/>
-    <hyperlink ref="C34" r:id="rId11" xr:uid="{DBDCD06D-2923-4218-BC97-ABE03390F1D7}"/>
-    <hyperlink ref="C35" r:id="rId12" xr:uid="{2AB62B2B-68E1-40FD-B878-E1B53BE55C54}"/>
-    <hyperlink ref="C20" r:id="rId13" xr:uid="{1FE273A7-C2F0-4349-9B1A-4442668BA296}"/>
-    <hyperlink ref="C36" r:id="rId14" xr:uid="{9381CA16-CF22-4437-ACD7-1E1796619196}"/>
-    <hyperlink ref="C43" r:id="rId15" xr:uid="{8A309B9A-E247-4CBE-87BB-B85B0A69E7D8}"/>
-    <hyperlink ref="C17" r:id="rId16" xr:uid="{70D6EB93-C68C-4CDC-BF76-F41A8E2104DE}"/>
-    <hyperlink ref="C37" r:id="rId17" xr:uid="{4848D5FD-F053-4486-8E3E-D89C72341827}"/>
-    <hyperlink ref="C18" r:id="rId18" xr:uid="{8F35F983-AFB9-48AE-8283-EE20E0D257FF}"/>
-    <hyperlink ref="C44" r:id="rId19" xr:uid="{2E7B406A-B501-4CFA-810E-97CD43405EB3}"/>
-    <hyperlink ref="C45" r:id="rId20" xr:uid="{42C99594-AAE8-4E35-91FC-5AB94011BC96}"/>
-    <hyperlink ref="C7" r:id="rId21" xr:uid="{FEEF8F34-0FC0-4F46-9A43-8C7A538DDB05}"/>
-    <hyperlink ref="C3" r:id="rId22" xr:uid="{44209C97-1064-412A-A07E-09A8319F0DC3}"/>
-    <hyperlink ref="C46" r:id="rId23" xr:uid="{E3C2BCAA-B2C5-4140-AFAB-699F12F824F8}"/>
-    <hyperlink ref="C21" r:id="rId24" xr:uid="{6775C434-C635-41C4-A4A2-85E4FC7BF7B4}"/>
-    <hyperlink ref="C47" r:id="rId25" xr:uid="{9B49F270-4E7E-4719-B7C6-A6C10D0755E1}"/>
-    <hyperlink ref="C48" r:id="rId26" xr:uid="{39424440-C765-4B0E-A77A-F13B8E6025C0}"/>
-    <hyperlink ref="C49" r:id="rId27" xr:uid="{5E9507EB-C8C0-4121-AAC7-F797B1919E5B}"/>
-    <hyperlink ref="C22" r:id="rId28" xr:uid="{240C280F-C6A6-4AAF-B749-C521E8C36A54}"/>
-    <hyperlink ref="C23" r:id="rId29" xr:uid="{D9FF37C8-1533-4CAF-8493-CEE43B120B13}"/>
-    <hyperlink ref="C19" r:id="rId30" xr:uid="{5E303B2A-86FF-4460-A167-90ECDB6A9B0E}"/>
-    <hyperlink ref="C14" r:id="rId31" xr:uid="{DCF47709-2C3C-7141-8672-BC6FE078F3C8}"/>
-    <hyperlink ref="C51" r:id="rId32" xr:uid="{C6722E39-8D6E-498B-956C-E13CEF15DD91}"/>
-    <hyperlink ref="C52" r:id="rId33" xr:uid="{B352DAFD-8E59-403E-9531-64C53F63C44F}"/>
-    <hyperlink ref="C4" r:id="rId34" xr:uid="{57AE4192-3C88-48E0-8269-EB3CD1E6C2A8}"/>
-    <hyperlink ref="C25" r:id="rId35" xr:uid="{BCE8B85C-7F7F-4303-ADF2-DC9FFE1ACA40}"/>
-    <hyperlink ref="C28" r:id="rId36" xr:uid="{FCCF507F-3E72-4788-BAF6-6DA009D7394C}"/>
-    <hyperlink ref="C29" r:id="rId37" xr:uid="{A289D90F-20D8-450E-9AB0-557D85EA314F}"/>
-    <hyperlink ref="C30" r:id="rId38" xr:uid="{26E44FBF-4211-4D7A-A9A8-A4D19F2C8064}"/>
-    <hyperlink ref="C31" r:id="rId39" xr:uid="{312F4EBC-D623-4233-A423-601AA8543EEC}"/>
-    <hyperlink ref="C2" r:id="rId40" xr:uid="{D5CE1D64-E6A0-489F-80ED-CD86A9700059}"/>
-    <hyperlink ref="C50" r:id="rId41" xr:uid="{BEDA0D96-EA07-4DA1-AA12-AF21965BE98F}"/>
-    <hyperlink ref="C8" r:id="rId42" xr:uid="{193C1629-FF53-4D82-89AC-4951C024A328}"/>
-    <hyperlink ref="C9" r:id="rId43" xr:uid="{99D04A76-6CF1-4E21-8E24-08577B6D8EDD}"/>
-    <hyperlink ref="C24" r:id="rId44" xr:uid="{5BD7097C-F4F9-4E7C-928E-9F7DB32C56BE}"/>
-    <hyperlink ref="C53" r:id="rId45" xr:uid="{D9D7F3DC-EB7B-496A-957B-D642222B2184}"/>
-    <hyperlink ref="C54" r:id="rId46" xr:uid="{57026629-D559-44AA-99C0-D6812C6C5753}"/>
-    <hyperlink ref="C55" r:id="rId47" xr:uid="{5502A002-2A4E-41BD-8753-3F8E6A3FE3AD}"/>
-    <hyperlink ref="C56" r:id="rId48" xr:uid="{E40631A0-C61A-4DA4-B1AD-AF3EEC89DC51}"/>
-    <hyperlink ref="C57" r:id="rId49" xr:uid="{6B54A3F6-9175-4567-9381-B34FE03B16B6}"/>
-    <hyperlink ref="C58" r:id="rId50" xr:uid="{CC0D3221-A564-41AD-89C3-B9BD2DB862AF}"/>
-    <hyperlink ref="C59" r:id="rId51" xr:uid="{99B08B75-DF0E-4727-AA58-7972572A4E0F}"/>
-    <hyperlink ref="C60" r:id="rId52" xr:uid="{051C51F6-F07A-4545-83B8-86BF9E184DDC}"/>
-    <hyperlink ref="C61" r:id="rId53" xr:uid="{E81E296F-58C8-46D4-AF45-51F0E6BB9EFE}"/>
-    <hyperlink ref="C62" r:id="rId54" xr:uid="{6ED15BE1-DB86-44F1-9E4E-AEF7035A9A0A}"/>
-    <hyperlink ref="C63" r:id="rId55" xr:uid="{E0165319-1A0E-477E-B52D-E0057A44F615}"/>
-    <hyperlink ref="C10" r:id="rId56" xr:uid="{708A4E17-0586-427D-B106-9DB06F0F1341}"/>
-    <hyperlink ref="C64" r:id="rId57" xr:uid="{418027A3-A711-41F9-A5A7-CEEDCA43C269}"/>
-    <hyperlink ref="C65" r:id="rId58" xr:uid="{2A5635ED-DF81-EA4B-8D6E-86E01201A208}"/>
-    <hyperlink ref="C66" r:id="rId59" xr:uid="{1D8E51E0-BCC9-4309-B1E7-DFBED221BB48}"/>
+    <hyperlink ref="G13" r:id="rId1" xr:uid="{03E1A70C-9821-4C3B-A9B6-160CD7AF2B09}"/>
+    <hyperlink ref="G40" r:id="rId2" xr:uid="{531EE4B2-7829-49A7-B0F8-4B3472382EA4}"/>
+    <hyperlink ref="G27" r:id="rId3" xr:uid="{7A9195DE-837C-4E4B-83AD-B0EA94AA9FA1}"/>
+    <hyperlink ref="G41" r:id="rId4" xr:uid="{612BBAC4-56D4-4C02-B4C7-B368F667A27C}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{333EA777-2839-46C2-84E0-DF880DD110E4}"/>
+    <hyperlink ref="G42" r:id="rId6" xr:uid="{237D8F06-D0E5-46CC-A9C8-1F3398D18D32}"/>
+    <hyperlink ref="G7" r:id="rId7" xr:uid="{D01877CE-88BD-4D26-ADB8-B843361BD8F3}"/>
+    <hyperlink ref="G28" r:id="rId8" xr:uid="{E8E1EE36-A43F-4E6C-82EB-1B0EBCACF359}"/>
+    <hyperlink ref="G14" r:id="rId9" xr:uid="{ED394140-5C5A-4D98-BABA-7E505B356F48}"/>
+    <hyperlink ref="G17" r:id="rId10" xr:uid="{F68A6A90-12CC-4DB9-9BAE-B28F89978E8C}"/>
+    <hyperlink ref="G35" r:id="rId11" xr:uid="{98C294E3-A48D-4594-B405-008C9E3CDD2A}"/>
+    <hyperlink ref="G36" r:id="rId12" xr:uid="{698A3DCC-47FA-4E44-A0D1-5C85BF30C0B8}"/>
+    <hyperlink ref="G21" r:id="rId13" xr:uid="{7FEEB4B8-4851-4D7A-8720-E079FDD9B514}"/>
+    <hyperlink ref="G37" r:id="rId14" xr:uid="{B3C0DDBE-12F0-4252-A852-C5597E14E6DA}"/>
+    <hyperlink ref="G43" r:id="rId15" xr:uid="{FB35CB07-01B3-4451-B1A0-20A364EF213B}"/>
+    <hyperlink ref="G18" r:id="rId16" xr:uid="{B3AC59A2-60F1-4E98-BFA2-0C861444D328}"/>
+    <hyperlink ref="G38" r:id="rId17" xr:uid="{07E9B401-F2CE-42BC-ABFF-BF4E0AB0015D}"/>
+    <hyperlink ref="G19" r:id="rId18" xr:uid="{3CF8884E-1A9D-4BEA-A8F2-122BC718C6B7}"/>
+    <hyperlink ref="G44" r:id="rId19" xr:uid="{10EA1663-D08A-4040-AA1A-6E1C3B398677}"/>
+    <hyperlink ref="G45" r:id="rId20" xr:uid="{D3065E3F-58FF-42B8-9872-52E1FEBF79FB}"/>
+    <hyperlink ref="G8" r:id="rId21" xr:uid="{766F30FF-AA0D-46E3-A00E-D3D682050740}"/>
+    <hyperlink ref="G4" r:id="rId22" xr:uid="{FAFEBE1E-4DC2-43F1-80E1-47D7A00E0F33}"/>
+    <hyperlink ref="G46" r:id="rId23" xr:uid="{4B76C52A-A416-41E5-96E1-621A4827E595}"/>
+    <hyperlink ref="G22" r:id="rId24" xr:uid="{9618E49D-1B83-4465-BF53-B8CCB1FA1C3B}"/>
+    <hyperlink ref="G47" r:id="rId25" xr:uid="{393D7858-4612-4954-8689-E81B76D587F3}"/>
+    <hyperlink ref="G48" r:id="rId26" xr:uid="{B667EDA2-9D85-40FA-B04C-F1F004BA3C42}"/>
+    <hyperlink ref="G49" r:id="rId27" xr:uid="{E0E0498D-7623-45D9-9DB5-B269BF2C8A31}"/>
+    <hyperlink ref="G23" r:id="rId28" xr:uid="{50051DD1-F2E3-4299-A438-7BC2EDC0163C}"/>
+    <hyperlink ref="G24" r:id="rId29" xr:uid="{77AABF80-91E8-4E99-B39E-55EA59EB5639}"/>
+    <hyperlink ref="G20" r:id="rId30" xr:uid="{88F5E632-5CAA-4B91-9BA6-7F2D4171B18C}"/>
+    <hyperlink ref="G15" r:id="rId31" xr:uid="{7BAAE701-01A6-4280-814C-DB3A65F0E9B3}"/>
+    <hyperlink ref="G51" r:id="rId32" xr:uid="{AC055807-CE47-439F-918C-4047CF13BE58}"/>
+    <hyperlink ref="G52" r:id="rId33" xr:uid="{88FBD14E-F8C1-4516-B669-B67A7F81309C}"/>
+    <hyperlink ref="G5" r:id="rId34" xr:uid="{FFF3946C-9411-45DB-B2CB-B4C926A7E2F1}"/>
+    <hyperlink ref="G26" r:id="rId35" xr:uid="{A27F1AB9-12F4-4E11-BEC6-98C82552685D}"/>
+    <hyperlink ref="G29" r:id="rId36" xr:uid="{A4CD9FF3-26DA-4CC7-8008-0B96CF799F98}"/>
+    <hyperlink ref="G30" r:id="rId37" xr:uid="{AEFCEF75-C631-49E1-BE88-EA8F6C3256DD}"/>
+    <hyperlink ref="G31" r:id="rId38" xr:uid="{230891D7-CB90-4BBF-9019-E401CF2181A0}"/>
+    <hyperlink ref="G32" r:id="rId39" xr:uid="{A945606A-7D5D-47AA-9224-F7D4BAAAC232}"/>
+    <hyperlink ref="G3" r:id="rId40" xr:uid="{2E83F20A-10F7-4988-A2DA-A011DF8D3DF3}"/>
+    <hyperlink ref="G50" r:id="rId41" xr:uid="{4E85C92C-301C-4A5E-B1B1-847BEFFEC4DD}"/>
+    <hyperlink ref="G9" r:id="rId42" xr:uid="{626F615E-7542-4F1B-AE91-18761113C241}"/>
+    <hyperlink ref="G10" r:id="rId43" xr:uid="{3F938749-3544-48FD-9011-060811A958D5}"/>
+    <hyperlink ref="G25" r:id="rId44" xr:uid="{DAB6F80A-27B2-4424-8000-9ACD7C6795F5}"/>
+    <hyperlink ref="G53" r:id="rId45" xr:uid="{703DAD60-5F66-49D1-99B4-056A6991E679}"/>
+    <hyperlink ref="G54" r:id="rId46" xr:uid="{51528D65-3602-489E-88A6-602E08B5A40D}"/>
+    <hyperlink ref="G55" r:id="rId47" xr:uid="{74CCB431-C0A2-429E-9214-406DD1B81BDB}"/>
+    <hyperlink ref="G56" r:id="rId48" xr:uid="{9D01C76B-D7CA-4E7A-911E-7CC9B3A76C4C}"/>
+    <hyperlink ref="G57" r:id="rId49" xr:uid="{A20C7B44-4E71-4529-A061-4152690500C7}"/>
+    <hyperlink ref="G58" r:id="rId50" xr:uid="{1F6D43A2-46A0-4A39-A754-7EAA0C9B54D9}"/>
+    <hyperlink ref="G59" r:id="rId51" xr:uid="{03888E11-9C8A-4506-9D61-715CE09C2CC8}"/>
+    <hyperlink ref="G60" r:id="rId52" xr:uid="{E9048606-BFA9-4F7A-B92D-046E72AAF72E}"/>
+    <hyperlink ref="G61" r:id="rId53" xr:uid="{87B16591-D89F-41CD-96AD-8E3DEBFFA995}"/>
+    <hyperlink ref="G62" r:id="rId54" xr:uid="{3436D05B-5786-40A9-90F8-2B01626317B0}"/>
+    <hyperlink ref="G63" r:id="rId55" xr:uid="{3F45C98D-F660-421B-8B20-400F36F8C2E8}"/>
+    <hyperlink ref="G11" r:id="rId56" xr:uid="{44A13BDE-F305-4546-879B-FEB12A43FAC4}"/>
+    <hyperlink ref="G64" r:id="rId57" xr:uid="{F9AC3E17-92B5-4DD7-91DB-6A62693209D7}"/>
+    <hyperlink ref="G65" r:id="rId58" xr:uid="{48F24171-BB87-48DA-9A02-F01A89AAD767}"/>
+    <hyperlink ref="G66" r:id="rId59" xr:uid="{15164EDA-26F1-4878-A505-6E35BA2A86DA}"/>
+    <hyperlink ref="G39" r:id="rId60" xr:uid="{EDAACF52-3506-4072-BF6F-23C230C797CA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId61"/>
+  <tableParts count="1">
+    <tablePart r:id="rId62"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/_data/MVLS LTS ORCiD.xlsx
+++ b/_data/MVLS LTS ORCiD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gla-my.sharepoint.com/personal/emily_nordmann_glasgow_ac_uk/Documents/04_Leadership-and-Governance/mvls-lts/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53DA4A6A-76E6-433A-A22F-A0B8FBCD6F50}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71ABB60B-ED6E-4FCB-B08E-0B276BD5FE5A}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="153">
   <si>
     <t>Id</t>
   </si>
@@ -484,13 +484,25 @@
   </si>
   <si>
     <t>https://orcid.org/0000-0001-9284-5518</t>
+  </si>
+  <si>
+    <t>Ellie.Wigham@glasgow.ac.uk</t>
+  </si>
+  <si>
+    <t>Ellie Wigham</t>
+  </si>
+  <si>
+    <t>School of Biodiversity, One Health, &amp; Veterinary Medicine</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0003-3616-7745</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -528,13 +540,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -570,8 +581,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:G66" totalsRowShown="0">
-  <autoFilter ref="A1:G66" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:G67" totalsRowShown="0">
+  <autoFilter ref="A1:G67" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="4">
       <extLst>
@@ -626,7 +637,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="KVxybjp2UE-B8i4lTwEzyKAHhjrab3lLkx60RR1iKjNUOTVNTEMwVE02SEhMQ0ZZODExQktLVThBSiQlQCNjPTEu" isFormConnected="1" maxResponseId="2" latestEventMarker="1">
+      <xlmsforms:msForm id="KVxybjp2UE-B8i4lTwEzyKAHhjrab3lLkx60RR1iKjNUOTVNTEMwVE02SEhMQ0ZZODExQktLVThBSiQlQCNjPTEu" isFormConnected="1" maxResponseId="3" latestEventMarker="2">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -937,13 +948,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G66"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:G67"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="7" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -966,7 +977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -989,8 +1000,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="3"/>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
         <v>11</v>
@@ -998,12 +1008,11 @@
       <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="3"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
         <v>14</v>
@@ -1011,12 +1020,11 @@
       <c r="F4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="3"/>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
         <v>16</v>
@@ -1024,12 +1032,11 @@
       <c r="F5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="3"/>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
         <v>18</v>
@@ -1037,12 +1044,11 @@
       <c r="F6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="3"/>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
         <v>21</v>
@@ -1050,12 +1056,11 @@
       <c r="F7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="3"/>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
         <v>23</v>
@@ -1063,12 +1068,11 @@
       <c r="F8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="3"/>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
         <v>25</v>
@@ -1076,12 +1080,11 @@
       <c r="F9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="3"/>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
         <v>27</v>
@@ -1089,12 +1092,11 @@
       <c r="F10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="3"/>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
         <v>30</v>
@@ -1102,12 +1104,11 @@
       <c r="F11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="3"/>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
         <v>32</v>
@@ -1119,8 +1120,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="3"/>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
         <v>35</v>
@@ -1128,12 +1128,11 @@
       <c r="F13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="3"/>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
         <v>38</v>
@@ -1141,12 +1140,11 @@
       <c r="F14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="3"/>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
         <v>40</v>
@@ -1154,12 +1152,11 @@
       <c r="F15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="3"/>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
         <v>42</v>
@@ -1171,8 +1168,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="3"/>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
         <v>44</v>
@@ -1180,12 +1176,11 @@
       <c r="F17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="3"/>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
         <v>46</v>
@@ -1193,12 +1188,11 @@
       <c r="F18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="3"/>
+    <row r="19" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
         <v>48</v>
@@ -1206,12 +1200,11 @@
       <c r="F19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="3"/>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
         <v>50</v>
@@ -1219,12 +1212,11 @@
       <c r="F20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="3"/>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
         <v>52</v>
@@ -1232,12 +1224,11 @@
       <c r="F21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="3"/>
+    <row r="22" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
         <v>55</v>
@@ -1245,12 +1236,11 @@
       <c r="F22" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="3"/>
+    <row r="23" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
         <v>57</v>
@@ -1258,12 +1248,11 @@
       <c r="F23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="3"/>
+    <row r="24" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
         <v>59</v>
@@ -1271,12 +1260,11 @@
       <c r="F24" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="3"/>
+    <row r="25" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
         <v>61</v>
@@ -1284,12 +1272,11 @@
       <c r="F25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="3"/>
+    <row r="26" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
         <v>64</v>
@@ -1297,12 +1284,11 @@
       <c r="F26" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="3"/>
+    <row r="27" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D27" s="1"/>
       <c r="E27" s="1" t="s">
         <v>66</v>
@@ -1310,12 +1296,11 @@
       <c r="F27" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="3"/>
+    <row r="28" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
         <v>69</v>
@@ -1323,12 +1308,11 @@
       <c r="F28" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="3"/>
+    <row r="29" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
         <v>71</v>
@@ -1336,12 +1320,11 @@
       <c r="F29" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="3"/>
+    <row r="30" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D30" s="1"/>
       <c r="E30" s="1" t="s">
         <v>73</v>
@@ -1349,12 +1332,11 @@
       <c r="F30" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="3"/>
+    <row r="31" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
         <v>75</v>
@@ -1362,12 +1344,11 @@
       <c r="F31" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="3"/>
+    <row r="32" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
         <v>77</v>
@@ -1375,12 +1356,11 @@
       <c r="F32" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="3"/>
+    <row r="33" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D33" s="1"/>
       <c r="E33" s="1" t="s">
         <v>79</v>
@@ -1392,8 +1372,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="3"/>
+    <row r="34" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D34" s="1"/>
       <c r="E34" s="1" t="s">
         <v>82</v>
@@ -1405,8 +1384,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="3"/>
+    <row r="35" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D35" s="1"/>
       <c r="E35" s="1" t="s">
         <v>84</v>
@@ -1414,12 +1392,11 @@
       <c r="F35" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="3"/>
+    <row r="36" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D36" s="1"/>
       <c r="E36" s="1" t="s">
         <v>86</v>
@@ -1427,12 +1404,11 @@
       <c r="F36" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="3"/>
+    <row r="37" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D37" s="1"/>
       <c r="E37" s="1" t="s">
         <v>88</v>
@@ -1440,12 +1416,11 @@
       <c r="F37" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="3"/>
+    <row r="38" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
         <v>90</v>
@@ -1453,12 +1428,11 @@
       <c r="F38" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="3"/>
+    <row r="39" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D39" s="1"/>
       <c r="E39" s="1" t="s">
         <v>92</v>
@@ -1466,12 +1440,11 @@
       <c r="F39" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="G39" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="3"/>
+    <row r="40" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D40" s="1"/>
       <c r="E40" s="1" t="s">
         <v>94</v>
@@ -1479,12 +1452,11 @@
       <c r="F40" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="3"/>
+    <row r="41" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D41" s="1"/>
       <c r="E41" s="1" t="s">
         <v>96</v>
@@ -1492,12 +1464,11 @@
       <c r="F41" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="3"/>
+    <row r="42" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
         <v>98</v>
@@ -1505,12 +1476,11 @@
       <c r="F42" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="3"/>
+    <row r="43" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D43" s="1"/>
       <c r="E43" s="1" t="s">
         <v>100</v>
@@ -1518,12 +1488,11 @@
       <c r="F43" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="3"/>
+    <row r="44" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D44" s="1"/>
       <c r="E44" s="1" t="s">
         <v>102</v>
@@ -1531,12 +1500,11 @@
       <c r="F44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="3"/>
+    <row r="45" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D45" s="1"/>
       <c r="E45" s="1" t="s">
         <v>104</v>
@@ -1544,12 +1512,11 @@
       <c r="F45" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="3"/>
+    <row r="46" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D46" s="1"/>
       <c r="E46" s="1" t="s">
         <v>106</v>
@@ -1557,12 +1524,11 @@
       <c r="F46" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="3"/>
+    <row r="47" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D47" s="1"/>
       <c r="E47" s="1" t="s">
         <v>108</v>
@@ -1570,12 +1536,11 @@
       <c r="F47" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="3" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="3"/>
+    <row r="48" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D48" s="1"/>
       <c r="E48" s="1" t="s">
         <v>110</v>
@@ -1583,12 +1548,11 @@
       <c r="F48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G48" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="3"/>
+    <row r="49" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D49" s="1"/>
       <c r="E49" s="1" t="s">
         <v>112</v>
@@ -1596,12 +1560,11 @@
       <c r="F49" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="G49" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="3"/>
+    <row r="50" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D50" s="1"/>
       <c r="E50" s="1" t="s">
         <v>114</v>
@@ -1609,12 +1572,11 @@
       <c r="F50" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="G50" s="3" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="3"/>
+    <row r="51" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D51" s="1"/>
       <c r="E51" s="1" t="s">
         <v>116</v>
@@ -1622,12 +1584,11 @@
       <c r="F51" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G51" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="3"/>
+    <row r="52" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D52" s="1"/>
       <c r="E52" s="1" t="s">
         <v>119</v>
@@ -1635,12 +1596,11 @@
       <c r="F52" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="3"/>
+    <row r="53" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D53" s="1"/>
       <c r="E53" s="1" t="s">
         <v>121</v>
@@ -1648,12 +1608,11 @@
       <c r="F53" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="G53" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="3"/>
+    <row r="54" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D54" s="1"/>
       <c r="E54" s="1" t="s">
         <v>123</v>
@@ -1661,12 +1620,11 @@
       <c r="F54" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G54" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="3"/>
+    <row r="55" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D55" s="1"/>
       <c r="E55" s="1" t="s">
         <v>125</v>
@@ -1674,12 +1632,11 @@
       <c r="F55" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="G55" s="3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="3"/>
+    <row r="56" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D56" s="1"/>
       <c r="E56" s="1" t="s">
         <v>127</v>
@@ -1687,12 +1644,11 @@
       <c r="F56" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G56" s="4" t="s">
+      <c r="G56" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="3"/>
+    <row r="57" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D57" s="1"/>
       <c r="E57" s="1" t="s">
         <v>129</v>
@@ -1700,12 +1656,11 @@
       <c r="F57" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="G57" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="3"/>
+    <row r="58" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D58" s="1"/>
       <c r="E58" s="1" t="s">
         <v>131</v>
@@ -1713,12 +1668,11 @@
       <c r="F58" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="G58" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="3"/>
+    <row r="59" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D59" s="1"/>
       <c r="E59" s="1" t="s">
         <v>132</v>
@@ -1726,12 +1680,11 @@
       <c r="F59" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G59" s="4" t="s">
+      <c r="G59" s="3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="3"/>
+    <row r="60" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D60" s="1"/>
       <c r="E60" s="1" t="s">
         <v>134</v>
@@ -1739,12 +1692,11 @@
       <c r="F60" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G60" s="4" t="s">
+      <c r="G60" s="3" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="3"/>
+    <row r="61" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D61" s="1"/>
       <c r="E61" s="1" t="s">
         <v>137</v>
@@ -1752,12 +1704,11 @@
       <c r="F61" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G61" s="5" t="s">
+      <c r="G61" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="3"/>
+    <row r="62" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D62" s="1"/>
       <c r="E62" s="1" t="s">
         <v>139</v>
@@ -1765,12 +1716,11 @@
       <c r="F62" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G62" s="4" t="s">
+      <c r="G62" s="3" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="3"/>
+    <row r="63" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D63" s="1"/>
       <c r="E63" s="1" t="s">
         <v>141</v>
@@ -1778,12 +1728,11 @@
       <c r="F63" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G63" s="5" t="s">
+      <c r="G63" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="3"/>
+    <row r="64" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D64" s="1"/>
       <c r="E64" s="1" t="s">
         <v>143</v>
@@ -1791,12 +1740,11 @@
       <c r="F64" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G64" s="4" t="s">
+      <c r="G64" s="3" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
-      <c r="A65" s="3"/>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D65" s="1"/>
       <c r="E65" s="1" t="s">
         <v>145</v>
@@ -1804,12 +1752,11 @@
       <c r="F65" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G65" s="4" t="s">
+      <c r="G65" s="3" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="3"/>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D66" s="1"/>
       <c r="E66" s="1" t="s">
         <v>147</v>
@@ -1817,8 +1764,31 @@
       <c r="F66" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="G66" s="3" t="s">
         <v>148</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" s="4">
+        <v>3</v>
+      </c>
+      <c r="B67">
+        <v>46192.363819444399</v>
+      </c>
+      <c r="C67">
+        <v>46192.364421296297</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/_data/MVLS LTS ORCiD.xlsx
+++ b/_data/MVLS LTS ORCiD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gla-my.sharepoint.com/personal/emily_nordmann_glasgow_ac_uk/Documents/04_Leadership-and-Governance/mvls-lts/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71ABB60B-ED6E-4FCB-B08E-0B276BD5FE5A}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A388971-5ACC-410D-85FD-39C1563EE96A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="157">
   <si>
     <t>Id</t>
   </si>
@@ -496,6 +496,18 @@
   </si>
   <si>
     <t>https://orcid.org/0000-0003-3616-7745</t>
+  </si>
+  <si>
+    <t>Sarah.Meek@glasgow.ac.uk</t>
+  </si>
+  <si>
+    <t>Sarah Meek</t>
+  </si>
+  <si>
+    <t>School of Medicine, Dentistry, &amp; Nursing</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0001-8771-4185</t>
   </si>
 </sst>
 </file>
@@ -581,8 +593,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:G67" totalsRowShown="0">
-  <autoFilter ref="A1:G67" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:G68" totalsRowShown="0">
+  <autoFilter ref="A1:G68" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="4">
       <extLst>
@@ -637,7 +649,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="KVxybjp2UE-B8i4lTwEzyKAHhjrab3lLkx60RR1iKjNUOTVNTEMwVE02SEhMQ0ZZODExQktLVThBSiQlQCNjPTEu" isFormConnected="1" maxResponseId="3" latestEventMarker="2">
+      <xlmsforms:msForm id="KVxybjp2UE-B8i4lTwEzyKAHhjrab3lLkx60RR1iKjNUOTVNTEMwVE02SEhMQ0ZZODExQktLVThBSiQlQCNjPTEu" isFormConnected="1" maxResponseId="4" latestEventMarker="3">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -948,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="7" width="20" bestFit="1" customWidth="1"/>
@@ -1769,7 +1781,7 @@
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A67" s="4">
+      <c r="A67">
         <v>3</v>
       </c>
       <c r="B67">
@@ -1789,6 +1801,29 @@
       </c>
       <c r="G67" s="3" t="s">
         <v>152</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" s="4">
+        <v>4</v>
+      </c>
+      <c r="B68">
+        <v>46194.531956018502</v>
+      </c>
+      <c r="C68">
+        <v>46194.532291666699</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/_data/MVLS LTS ORCiD.xlsx
+++ b/_data/MVLS LTS ORCiD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30413"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gla-my.sharepoint.com/personal/emily_nordmann_glasgow_ac_uk/Documents/04_Leadership-and-Governance/mvls-lts/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A388971-5ACC-410D-85FD-39C1563EE96A}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7197BECC-1FC6-4ED4-8413-47E3E98CD32B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="170">
   <si>
     <t>Id</t>
   </si>
@@ -508,13 +508,52 @@
   </si>
   <si>
     <t>https://orcid.org/0000-0001-8771-4185</t>
+  </si>
+  <si>
+    <t>Jenny.Clancy@glasgow.ac.uk</t>
+  </si>
+  <si>
+    <t>Jenny Clancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://orcid.org/0000-0002-1568-2046 </t>
+  </si>
+  <si>
+    <t>Jennifer.Hammond@glasgow.ac.uk</t>
+  </si>
+  <si>
+    <t>Jennifer Hammond</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0009-0002-1963-2545</t>
+  </si>
+  <si>
+    <t>Courtney.TaylorBrowneLuka@glasgow.ac.uk</t>
+  </si>
+  <si>
+    <t>Courtney Taylor Browne Luka</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-2819-0673</t>
+  </si>
+  <si>
+    <t>Sandy.Wilson@glasgow.ac.uk</t>
+  </si>
+  <si>
+    <t>Sandy Wilson</t>
+  </si>
+  <si>
+    <t>Graduate School</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-9313-4280</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -593,8 +632,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:G68" totalsRowShown="0">
-  <autoFilter ref="A1:G68" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:G72" totalsRowShown="0">
+  <autoFilter ref="A1:G72" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="4">
       <extLst>
@@ -649,7 +688,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="KVxybjp2UE-B8i4lTwEzyKAHhjrab3lLkx60RR1iKjNUOTVNTEMwVE02SEhMQ0ZZODExQktLVThBSiQlQCNjPTEu" isFormConnected="1" maxResponseId="4" latestEventMarker="3">
+      <xlmsforms:msForm id="KVxybjp2UE-B8i4lTwEzyKAHhjrab3lLkx60RR1iKjNUOTVNTEMwVE02SEhMQ0ZZODExQktLVThBSiQlQCNjPTEu" isFormConnected="1" maxResponseId="8" latestEventMarker="7">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -960,13 +999,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G72"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="7" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -989,7 +1028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1012,7 +1051,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7">
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
         <v>11</v>
@@ -1024,7 +1063,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7">
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
         <v>14</v>
@@ -1036,7 +1075,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7">
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
         <v>16</v>
@@ -1048,7 +1087,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7">
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
         <v>18</v>
@@ -1060,7 +1099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7">
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
         <v>21</v>
@@ -1072,7 +1111,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7">
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
         <v>23</v>
@@ -1084,7 +1123,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7">
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
         <v>25</v>
@@ -1096,7 +1135,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7">
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
         <v>27</v>
@@ -1108,7 +1147,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7">
       <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
         <v>30</v>
@@ -1120,7 +1159,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7">
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
         <v>32</v>
@@ -1132,7 +1171,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7">
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
         <v>35</v>
@@ -1144,7 +1183,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7">
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
         <v>38</v>
@@ -1156,7 +1195,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7">
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
         <v>40</v>
@@ -1168,7 +1207,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7">
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
         <v>42</v>
@@ -1180,7 +1219,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="4:7">
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
         <v>44</v>
@@ -1192,7 +1231,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="4:7">
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
         <v>46</v>
@@ -1204,7 +1243,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="4:7">
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
         <v>48</v>
@@ -1216,7 +1255,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="4:7">
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
         <v>50</v>
@@ -1228,7 +1267,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="4:7">
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
         <v>52</v>
@@ -1240,7 +1279,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="4:7">
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
         <v>55</v>
@@ -1252,7 +1291,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="4:7">
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
         <v>57</v>
@@ -1264,7 +1303,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="4:7">
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
         <v>59</v>
@@ -1276,7 +1315,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="4:7">
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
         <v>61</v>
@@ -1288,7 +1327,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="4:7">
       <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
         <v>64</v>
@@ -1300,7 +1339,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="4:7">
       <c r="D27" s="1"/>
       <c r="E27" s="1" t="s">
         <v>66</v>
@@ -1312,7 +1351,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="4:7">
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
         <v>69</v>
@@ -1324,7 +1363,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="4:7">
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
         <v>71</v>
@@ -1336,7 +1375,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="4:7">
       <c r="D30" s="1"/>
       <c r="E30" s="1" t="s">
         <v>73</v>
@@ -1348,7 +1387,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="4:7">
       <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
         <v>75</v>
@@ -1360,7 +1399,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="4:7">
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
         <v>77</v>
@@ -1372,7 +1411,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="4:7">
       <c r="D33" s="1"/>
       <c r="E33" s="1" t="s">
         <v>79</v>
@@ -1384,7 +1423,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="4:7">
       <c r="D34" s="1"/>
       <c r="E34" s="1" t="s">
         <v>82</v>
@@ -1396,7 +1435,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="4:7">
       <c r="D35" s="1"/>
       <c r="E35" s="1" t="s">
         <v>84</v>
@@ -1408,7 +1447,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="36" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="4:7">
       <c r="D36" s="1"/>
       <c r="E36" s="1" t="s">
         <v>86</v>
@@ -1420,7 +1459,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="37" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="4:7">
       <c r="D37" s="1"/>
       <c r="E37" s="1" t="s">
         <v>88</v>
@@ -1432,7 +1471,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="38" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="4:7">
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
         <v>90</v>
@@ -1444,7 +1483,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="4:7">
       <c r="D39" s="1"/>
       <c r="E39" s="1" t="s">
         <v>92</v>
@@ -1456,7 +1495,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="4:7">
       <c r="D40" s="1"/>
       <c r="E40" s="1" t="s">
         <v>94</v>
@@ -1468,7 +1507,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="41" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="4:7">
       <c r="D41" s="1"/>
       <c r="E41" s="1" t="s">
         <v>96</v>
@@ -1480,7 +1519,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="42" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="4:7">
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
         <v>98</v>
@@ -1492,7 +1531,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="4:7">
       <c r="D43" s="1"/>
       <c r="E43" s="1" t="s">
         <v>100</v>
@@ -1504,7 +1543,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="4:7">
       <c r="D44" s="1"/>
       <c r="E44" s="1" t="s">
         <v>102</v>
@@ -1516,7 +1555,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="4:7">
       <c r="D45" s="1"/>
       <c r="E45" s="1" t="s">
         <v>104</v>
@@ -1528,7 +1567,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="4:7">
       <c r="D46" s="1"/>
       <c r="E46" s="1" t="s">
         <v>106</v>
@@ -1540,7 +1579,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="4:7">
       <c r="D47" s="1"/>
       <c r="E47" s="1" t="s">
         <v>108</v>
@@ -1552,7 +1591,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="48" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="4:7">
       <c r="D48" s="1"/>
       <c r="E48" s="1" t="s">
         <v>110</v>
@@ -1564,7 +1603,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="4:7">
       <c r="D49" s="1"/>
       <c r="E49" s="1" t="s">
         <v>112</v>
@@ -1576,7 +1615,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="50" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="4:7">
       <c r="D50" s="1"/>
       <c r="E50" s="1" t="s">
         <v>114</v>
@@ -1588,7 +1627,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="51" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="4:7">
       <c r="D51" s="1"/>
       <c r="E51" s="1" t="s">
         <v>116</v>
@@ -1600,7 +1639,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="52" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="4:7">
       <c r="D52" s="1"/>
       <c r="E52" s="1" t="s">
         <v>119</v>
@@ -1612,7 +1651,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="53" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="4:7">
       <c r="D53" s="1"/>
       <c r="E53" s="1" t="s">
         <v>121</v>
@@ -1624,7 +1663,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="54" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="4:7">
       <c r="D54" s="1"/>
       <c r="E54" s="1" t="s">
         <v>123</v>
@@ -1636,7 +1675,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="55" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="4:7">
       <c r="D55" s="1"/>
       <c r="E55" s="1" t="s">
         <v>125</v>
@@ -1648,7 +1687,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="56" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="4:7">
       <c r="D56" s="1"/>
       <c r="E56" s="1" t="s">
         <v>127</v>
@@ -1660,7 +1699,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="57" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="4:7">
       <c r="D57" s="1"/>
       <c r="E57" s="1" t="s">
         <v>129</v>
@@ -1672,7 +1711,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="4:7">
       <c r="D58" s="1"/>
       <c r="E58" s="1" t="s">
         <v>131</v>
@@ -1684,7 +1723,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="59" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="4:7">
       <c r="D59" s="1"/>
       <c r="E59" s="1" t="s">
         <v>132</v>
@@ -1696,7 +1735,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="60" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="4:7">
       <c r="D60" s="1"/>
       <c r="E60" s="1" t="s">
         <v>134</v>
@@ -1708,7 +1747,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="61" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="4:7">
       <c r="D61" s="1"/>
       <c r="E61" s="1" t="s">
         <v>137</v>
@@ -1720,7 +1759,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="62" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="4:7">
       <c r="D62" s="1"/>
       <c r="E62" s="1" t="s">
         <v>139</v>
@@ -1732,7 +1771,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="63" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="4:7">
       <c r="D63" s="1"/>
       <c r="E63" s="1" t="s">
         <v>141</v>
@@ -1744,7 +1783,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="64" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="4:7">
       <c r="D64" s="1"/>
       <c r="E64" s="1" t="s">
         <v>143</v>
@@ -1756,7 +1795,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7">
       <c r="D65" s="1"/>
       <c r="E65" s="1" t="s">
         <v>145</v>
@@ -1768,7 +1807,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7">
       <c r="D66" s="1"/>
       <c r="E66" s="1" t="s">
         <v>147</v>
@@ -1780,7 +1819,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7">
       <c r="A67">
         <v>3</v>
       </c>
@@ -1803,8 +1842,8 @@
         <v>152</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A68" s="4">
+    <row r="68" spans="1:7">
+      <c r="A68">
         <v>4</v>
       </c>
       <c r="B68">
@@ -1824,6 +1863,98 @@
       </c>
       <c r="G68" s="3" t="s">
         <v>156</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15">
+      <c r="A69" s="4">
+        <v>5</v>
+      </c>
+      <c r="B69">
+        <v>46217.6531944444</v>
+      </c>
+      <c r="C69">
+        <v>46217.6546296296</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15">
+      <c r="A70" s="4">
+        <v>6</v>
+      </c>
+      <c r="B70">
+        <v>46217.742696759298</v>
+      </c>
+      <c r="C70">
+        <v>46217.743993055599</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="15">
+      <c r="A71" s="4">
+        <v>7</v>
+      </c>
+      <c r="B71">
+        <v>46253.4205671296</v>
+      </c>
+      <c r="C71">
+        <v>46253.422476851803</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15">
+      <c r="A72" s="4">
+        <v>8</v>
+      </c>
+      <c r="B72">
+        <v>46254.5945601852</v>
+      </c>
+      <c r="C72">
+        <v>46254.595439814802</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
